--- a/output/latest/JPMRGDPF_DATA_LATEST.xlsx
+++ b/output/latest/JPMRGDPF_DATA_LATEST.xlsx
@@ -890,7 +890,7 @@
         <v>3.4</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>1.3</v>
@@ -1000,7 +1000,7 @@
         <v>3.1</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="D5" t="n">
         <v>1.6</v>

--- a/output/latest/JPMRGDPF_DATA_LATEST.xlsx
+++ b/output/latest/JPMRGDPF_DATA_LATEST.xlsx
@@ -801,7 +801,7 @@
         <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>1.5</v>
@@ -876,7 +876,7 @@
         <v>3.6</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AJ3" t="n">
         <v>2.1</v>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
         <v>4.7</v>
@@ -914,13 +914,13 @@
         <v>2.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
       </c>
       <c r="N4" t="n">
         <v>3.3</v>
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="R4" t="n">
         <v>4.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
         <v>5.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
         <v>1.9</v>
@@ -965,7 +965,7 @@
         <v>3.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AC4" t="n">
         <v>4.1</v>
@@ -974,7 +974,7 @@
         <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AF4" t="n">
         <v>8.199999999999999</v>
@@ -989,7 +989,7 @@
         <v>0.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -1024,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -1051,7 +1051,7 @@
         <v>0.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="U5" t="n">
         <v>1.9</v>
@@ -1075,7 +1075,7 @@
         <v>2.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
         <v>3.1</v>
